--- a/outputs/candidates/baseline/score_breakdown.xlsx
+++ b/outputs/candidates/baseline/score_breakdown.xlsx
@@ -609,10 +609,10 @@
         <v>2465</v>
       </c>
       <c r="Q2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -683,10 +683,10 @@
         <v>1</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="U3">
         <v>34</v>
@@ -748,13 +748,13 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T4">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="U4">
         <v>34</v>
@@ -813,7 +813,7 @@
         <v>2465</v>
       </c>
       <c r="Q5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>23</v>
       </c>
       <c r="S6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U6">
         <v>34</v>
